--- a/output/pdf_financials_xlsx/VAND.xlsx
+++ b/output/pdf_financials_xlsx/VAND.xlsx
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.267897</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.289798</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.267897</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.289798</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">

--- a/output/pdf_financials_xlsx/VAND.xlsx
+++ b/output/pdf_financials_xlsx/VAND.xlsx
@@ -977,10 +977,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.267897</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.267897</v>
@@ -995,10 +993,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -1013,10 +1009,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.267897</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.267897</v>
@@ -1031,10 +1025,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
@@ -1049,10 +1041,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -1067,10 +1057,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -1085,10 +1073,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
@@ -1103,10 +1089,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0</v>
@@ -1121,10 +1105,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -1139,10 +1121,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -1157,10 +1137,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -1175,10 +1153,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -1193,10 +1169,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -1211,10 +1185,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -1229,10 +1201,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -1267,10 +1237,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
@@ -1285,10 +1253,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
@@ -1303,10 +1269,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
@@ -1321,10 +1285,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
@@ -1339,10 +1301,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
@@ -1379,10 +1339,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -1397,10 +1355,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>0</v>
@@ -1415,10 +1371,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>0</v>
@@ -1433,10 +1387,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0</v>
@@ -1451,10 +1403,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -1469,10 +1419,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0</v>
@@ -1507,10 +1455,8 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>0.267897</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>0.267897</v>
@@ -1525,10 +1471,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0</v>
@@ -1543,10 +1487,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0</v>
@@ -1561,10 +1503,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -1579,10 +1519,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
@@ -1597,10 +1535,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.042811</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.042811</v>
@@ -1615,10 +1551,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0</v>
@@ -1633,10 +1567,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -1651,10 +1583,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -1669,10 +1599,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0</v>
@@ -1687,10 +1615,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>0</v>
@@ -1705,10 +1631,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0</v>
@@ -1723,10 +1647,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0</v>
@@ -1761,10 +1683,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -1779,10 +1699,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -1797,10 +1715,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -1837,10 +1753,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>0</v>
@@ -1855,10 +1769,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>0</v>
@@ -1873,10 +1785,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>0</v>
@@ -1891,10 +1801,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0</v>
@@ -1909,10 +1817,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0</v>
@@ -1947,10 +1853,8 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0.042811</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>0.042811</v>
@@ -1965,10 +1869,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.245522</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.245522</v>
@@ -1983,10 +1885,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0</v>
@@ -2001,10 +1901,8 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-0.058191</v>
       </c>
       <c r="C90" s="3" t="n">
         <v>-0.058191</v>
@@ -2019,10 +1917,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -2037,10 +1933,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0</v>
@@ -2055,10 +1949,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>0</v>
@@ -2073,10 +1965,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.225086</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>0.225086</v>
@@ -2091,10 +1981,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>0</v>
@@ -2109,10 +1997,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.225086</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>0.225086</v>
@@ -2127,10 +2013,8 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.840196045495097</v>
       </c>
       <c r="C97" s="3" t="n">
         <v>0.840196045495097</v>
@@ -2827,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4248,10 +4132,8 @@
           <t>CashAndCashEquivalents</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E44" s="5" t="n">
+        <v>0.267897</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>0.267897</v>
@@ -4316,10 +4198,8 @@
           <t>TotalAssets</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E46" s="5" t="n">
+        <v>0.267897</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>0.267897</v>
@@ -4349,10 +4229,8 @@
           <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E47" s="5" t="n">
+        <v>0.042811</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>0.042811</v>
@@ -4382,10 +4260,8 @@
           <t>TotalLiabilities</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="5" t="n">
+        <v>0.042811</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>0.042811</v>
@@ -4415,10 +4291,8 @@
           <t>CapitalStock</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="5" t="n">
+        <v>0.245522</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>0.245522</v>
@@ -4444,10 +4318,8 @@
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="5" t="n">
+        <v>0.037755</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0.037755</v>
@@ -4477,10 +4349,8 @@
           <t>RetainedEarnings</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E51" s="5" t="n">
+        <v>-0.058191</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>-0.058191</v>
@@ -4510,10 +4380,8 @@
           <t>StockholdersEquity</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" s="5" t="n">
+        <v>0.225086</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0.225086</v>
@@ -4543,10 +4411,8 @@
           <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" s="5" t="n">
+        <v>0.267897</v>
       </c>
       <c r="F53" s="5" t="n">
         <v>0.267897</v>
@@ -4558,28 +4424,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Shareholders’ equity</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>January 20, 2022, to December</t>
+          <t>Basis of presentation (Note</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E54" s="5" t="n">
+        <v>2e-06</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -4588,21 +4458,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Cash flows used in operating activities</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>January 20, 2022, to December</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -4614,7 +4476,7 @@
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.838096</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="56">
@@ -4625,15 +4487,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Cash flows used in operating activities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Net and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -4645,7 +4511,7 @@
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.330677</v>
+        <v>-0.838096</v>
       </c>
     </row>
     <row r="57">
@@ -4661,7 +4527,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gain on revaluation of vanadium</t>
+          <t>Unrealized foreign exchange gain</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4676,7 +4542,7 @@
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.881954</v>
+        <v>-0.330677</v>
       </c>
     </row>
     <row r="58">
@@ -4692,7 +4558,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Excess of fair value over net assets acquired 1</t>
+          <t>Gain on revaluation of vanadium</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4707,7 +4573,7 @@
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.5714129999999999</v>
+        <v>-0.881954</v>
       </c>
     </row>
     <row r="59">
@@ -4723,7 +4589,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Excess of fair value over net assets acquired 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -4738,7 +4604,7 @@
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.329716</v>
+        <v>0.5714129999999999</v>
       </c>
     </row>
     <row r="60">
@@ -4754,7 +4620,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Non-cash items total</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4769,7 +4635,7 @@
         </is>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-1.149598</v>
+        <v>0.329716</v>
       </c>
     </row>
     <row r="61">
@@ -4780,12 +4646,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Changes in working capital balances</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Prepaid assets</t>
+          <t>Non-cash items total</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4800,7 +4666,7 @@
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-5.385179</v>
+        <v>-1.149598</v>
       </c>
     </row>
     <row r="62">
@@ -4816,7 +4682,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sales tax receivable</t>
+          <t>Prepaid assets</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4831,7 +4697,7 @@
         </is>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.089281</v>
+        <v>-5.385179</v>
       </c>
     </row>
     <row r="63">
@@ -4847,14 +4713,10 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Sales tax receivable</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -4866,7 +4728,7 @@
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.451426</v>
+        <v>-0.089281</v>
       </c>
     </row>
     <row r="64">
@@ -4882,10 +4744,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Changes in working capital balances total</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -4897,7 +4763,7 @@
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-6.172632</v>
+        <v>0.451426</v>
       </c>
     </row>
     <row r="65">
@@ -4908,12 +4774,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities</t>
+          <t>Changes in working capital balances</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Purchases of vanadium</t>
+          <t>Changes in working capital balances total</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -4928,7 +4794,7 @@
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-9.830821</v>
+        <v>-6.172632</v>
       </c>
     </row>
     <row r="66">
@@ -4944,7 +4810,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cash acquired in qualifying transaction</t>
+          <t>Purchases of vanadium</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -4959,7 +4825,7 @@
         </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.109164</v>
+        <v>-9.830821</v>
       </c>
     </row>
     <row r="67">
@@ -4975,14 +4841,10 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cash flows used in investing activities total</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Cash acquired in qualifying transaction</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -4994,7 +4856,7 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-9.721657</v>
+        <v>0.109164</v>
       </c>
     </row>
     <row r="68">
@@ -5005,15 +4867,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Cash flows used in investing activities</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Proceeds from share issuance 5</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Cash flows used in investing activities total</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -5025,7 +4891,7 @@
         </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.463284</v>
+        <v>-9.721657</v>
       </c>
     </row>
     <row r="69">
@@ -5041,10 +4907,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Proceeds from private placement 5</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Proceeds from share issuance 5</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -5056,7 +4926,7 @@
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>22.12104</v>
+        <v>0.463284</v>
       </c>
     </row>
     <row r="70">
@@ -5072,12 +4942,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
+          <t>Proceeds from private placement 5</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5091,7 +4961,7 @@
         </is>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.467042</v>
+        <v>22.12104</v>
       </c>
     </row>
     <row r="71">
@@ -5107,12 +4977,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities total</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5126,7 +4996,7 @@
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>22.117282</v>
+        <v>-0.467042</v>
       </c>
     </row>
     <row r="72">
@@ -5142,10 +5012,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Foreign exchange on cash</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Cash flows from financing activities total</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -5157,7 +5031,7 @@
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.134424</v>
+        <v>22.117282</v>
       </c>
     </row>
     <row r="73">
@@ -5173,14 +5047,10 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Foreign exchange on cash</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -5192,7 +5062,7 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>6.357417</v>
+        <v>0.134424</v>
       </c>
     </row>
     <row r="74">
@@ -5208,12 +5078,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of period</t>
+          <t>Net change in cash</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5226,10 +5096,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G74" s="5" t="n">
+        <v>6.357417</v>
       </c>
     </row>
     <row r="75">
@@ -5245,12 +5113,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of period $</t>
+          <t>Cash and cash equivalents, beginning of period</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5263,8 +5131,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G75" s="5" t="n">
-        <v>6.357417</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -5280,10 +5150,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Purchase of vanadium 4 $</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of period $</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -5295,7 +5169,7 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-5.31736</v>
+        <v>6.357417</v>
       </c>
     </row>
     <row r="77">
@@ -5311,7 +5185,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Shares issued for in-kind contribution 4,5</t>
+          <t>Purchase of vanadium 4 $</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -5326,7 +5200,7 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>5.31736</v>
+        <v>-5.31736</v>
       </c>
     </row>
     <row r="78">
@@ -5335,10 +5209,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2022 July</t>
+          <t>Shares issued for in-kind contribution 4,5</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -5347,11 +5225,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F78" s="5" t="n">
-        <v>0.002021</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>5.31736</v>
       </c>
     </row>
     <row r="79">
@@ -5360,31 +5240,23 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Net loss for the period</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>2022 July</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-0.058191</v>
+        <v>0.002021</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.045313</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="80">
@@ -5395,17 +5267,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Non-cash expenses</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Net loss for the period</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5414,12 +5286,10 @@
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.028388</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.058191</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>-0.045313</v>
       </c>
     </row>
     <row r="81">
@@ -5430,17 +5300,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-cash expenses</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5448,13 +5318,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>-0.065938</v>
+      <c r="F81" s="5" t="n">
+        <v>0.028388</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -5465,25 +5335,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities related to operating</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities related to operating activities</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F82" s="5" t="n">
-        <v>0.009920999999999999</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.060777</v>
+        <v>-0.065938</v>
       </c>
     </row>
     <row r="83">
@@ -5499,24 +5375,20 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Accounts payable and accrued liabilities related to operating activities</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>-0.019882</v>
+        <v>0.009920999999999999</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.050474</v>
+        <v>0.060777</v>
       </c>
     </row>
     <row r="84">
@@ -5527,17 +5399,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Accounts payable and accrued liabilities related to operating</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Payments for share issuance costs</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5546,10 +5418,10 @@
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.07222099999999999</v>
+        <v>-0.019882</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.03289</v>
+        <v>-0.050474</v>
       </c>
     </row>
     <row r="85">
@@ -5565,12 +5437,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Proceeds from sale of shares</t>
+          <t>Payments for share issuance costs</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5579,12 +5451,10 @@
         </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.07222099999999999</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-0.03289</v>
       </c>
     </row>
     <row r="86">
@@ -5600,12 +5470,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Net cash (used in) provided by financing activities</t>
+          <t>Proceeds from sale of shares</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5614,10 +5484,12 @@
         </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.287779</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>-0.03289</v>
+        <v>0.36</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -5633,12 +5505,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Change in cash during the period</t>
+          <t>Net cash (used in) provided by financing activities</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5647,10 +5519,10 @@
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.267897</v>
+        <v>0.287779</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.08336399999999999</v>
+        <v>-0.03289</v>
       </c>
     </row>
     <row r="88">
@@ -5666,12 +5538,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Change in cash during the period</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5679,13 +5551,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F88" s="5" t="n">
+        <v>0.267897</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.267897</v>
+        <v>-0.08336399999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5701,12 +5571,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cash, end of period</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5714,11 +5584,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" s="5" t="n">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n">
         <v>0.267897</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>0.184533</v>
       </c>
     </row>
     <row r="90">
@@ -5729,25 +5601,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Non-cash investing and financing activities</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>In addition to $72,221 in share issuance costs paid in the period from incorporation on November 26, 2020 to July</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Cash, end of period</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.002021</v>
+        <v>0.267897</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.184533</v>
       </c>
     </row>
     <row r="91">
@@ -5763,7 +5639,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>initial public offering. Additionally, $32,890 in share issuance costs were included in accounts payable and accrued liabilities as at July 31, 2021 and were paid during the year ended July</t>
+          <t>In addition to $72,221 in share issuance costs paid in the period from incorporation on November 26, 2020 to July</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -5773,7 +5649,7 @@
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.002022</v>
+        <v>0.002021</v>
       </c>
       <c r="G91" s="5" t="n">
         <v>3.1e-05</v>
@@ -5792,7 +5668,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>incorporation on November 26, 2020 to July</t>
+          <t>initial public offering. Additionally, $32,890 in share issuance costs were included in accounts payable and accrued liabilities as at July 31, 2021 and were paid during the year ended July</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -5802,7 +5678,7 @@
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.002021</v>
+        <v>0.002022</v>
       </c>
       <c r="G92" s="5" t="n">
         <v>3.1e-05</v>
@@ -5821,45 +5697,49 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>A total of $114,478 was recognized for share issuance costs in the period from incorporation on November 26, 2020 to incorporation on November 26, 2020 to July</t>
+          <t>incorporation on November 26, 2020 to July</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F93" s="5" t="n">
         <v>0.002021</v>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Non-cash investing and financing activities</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2022 July</t>
+          <t>A total of $114,478 was recognized for share issuance costs in the period from incorporation on November 26, 2020 to incorporation on November 26, 2020 to July</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>0.002021</v>
       </c>
-      <c r="G94" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -5868,25 +5748,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Administrative and corporate services (Note 6)</t>
+          <t>2022 July</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" s="5" t="n">
-        <v>0.00945</v>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.00945</v>
+        <v>0.002021</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.0189</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="96">
@@ -5902,22 +5780,18 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Transfer agent, shareholder communications, listing and filing fees</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Administrative and corporate services (Note 6)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" s="5" t="n">
-        <v>0.005271</v>
+        <v>0.00945</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.005271</v>
+        <v>0.00945</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.01509</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="97">
@@ -5933,22 +5807,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Transfer agent, shareholder communications, listing and filing fees</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0.014883</v>
+        <v>0.005271</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.014883</v>
+        <v>0.005271</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.011294</v>
+        <v>0.01509</v>
       </c>
     </row>
     <row r="98">
@@ -5964,18 +5838,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Office and sundry</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
-        <v>0.000199</v>
+        <v>0.014883</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.000199</v>
+        <v>0.014883</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>2.9e-05</v>
+        <v>0.011294</v>
       </c>
     </row>
     <row r="99">
@@ -5991,20 +5869,18 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 5 and 6)</t>
+          <t>Office and sundry</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" s="5" t="n">
-        <v>0.028388</v>
+        <v>0.000199</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.028388</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000199</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>2.9e-05</v>
       </c>
     </row>
     <row r="100">
@@ -6020,22 +5896,20 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the period</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Notes 5 and 6)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" s="5" t="n">
-        <v>-0.058191</v>
+        <v>0.028388</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>-0.058191</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>-0.045313</v>
+        <v>0.028388</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -6051,22 +5925,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share (Note 5)</t>
+          <t>Loss and comprehensive loss for the period</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-0.058191</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-0.058191</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.045313</v>
       </c>
     </row>
     <row r="102">
@@ -6077,29 +5951,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Shares     Amount        Reserves      Deficit          Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Balance, November 26, 2020 - - -</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per common share (Note 5)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="103">
@@ -6115,7 +5987,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Shares issued 3,450,000 360,000 -</t>
+          <t>Balance, November 26, 2020 - - -</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -6124,8 +5996,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F103" s="5" t="n">
-        <v>0.36</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6146,7 +6020,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Share issuance costs - (114,478) 9,367</t>
+          <t>Shares issued 3,450,000 360,000 -</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -6156,7 +6030,7 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.105111</v>
+        <v>0.36</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -6177,7 +6051,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 28,388</t>
+          <t>Share issuance costs - (114,478) 9,367</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -6187,7 +6061,7 @@
         </is>
       </c>
       <c r="F105" s="5" t="n">
-        <v>0.028388</v>
+        <v>-0.105111</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6208,24 +6082,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Net loss for the period - - -</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation - - 28,388</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
-        <v>-0.058191</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>-0.058191</v>
+        <v>0.028388</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -6241,17 +6113,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2021 3,450,000 245,522 37,755</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Net loss for the period - - -</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.225086</v>
+        <v>-0.058191</v>
       </c>
       <c r="G107" s="5" t="n">
         <v>-0.058191</v>
@@ -6270,24 +6146,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, July 31, 2021 3,450,000 245,522 37,755</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
-        <v>-0.045313</v>
+        <v>0.225086</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>-0.045313</v>
+        <v>-0.058191</v>
       </c>
     </row>
     <row r="109">
@@ -6303,20 +6175,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2022 3,450,000 245,522 37,755</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>0.179773</v>
+        <v>-0.045313</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>-0.103504</v>
+        <v>-0.045313</v>
       </c>
     </row>
     <row r="110">
@@ -6332,7 +6208,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Balance, November 26, 2020 - - - -</t>
+          <t>Balance, July 31, 2022 3,450,000 245,522 37,755</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -6341,15 +6217,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="5" t="n">
+        <v>0.179773</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>-0.103504</v>
       </c>
     </row>
     <row r="111">
@@ -6365,12 +6237,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Shares issued 3,450,000 360,000 - -</t>
+          <t>Balance, November 26, 2020 - - - -</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" s="5" t="n">
-        <v>0.36</v>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6396,12 +6270,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Share issuance costs - (114,478) 9,367 -</t>
+          <t>Shares issued 3,450,000 360,000 - -</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" s="5" t="n">
-        <v>-0.105111</v>
+        <v>0.36</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6427,12 +6301,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 28,388 -</t>
+          <t>Share issuance costs - (114,478) 9,367 -</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" s="5" t="n">
-        <v>0.028388</v>
+        <v>-0.105111</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -6458,12 +6332,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Net loss for the period - - - (58,191)</t>
+          <t>Share-based compensation - - 28,388 -</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" s="5" t="n">
-        <v>-0.058191</v>
+        <v>0.028388</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -6489,19 +6363,50 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2021 3,450,000 245,522 37,755 (58,191)</t>
+          <t>Net loss for the period - - - (58,191)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" s="5" t="n">
+        <v>-0.058191</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Shares     Amount        Reserves      Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2021 3,450,000 245,522 37,755 (58,191)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
         <v>0.225086</v>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
         <is>
           <t>-</t>
         </is>
